--- a/doc/source/_static/data/supporting_files/Terminology.xlsx
+++ b/doc/source/_static/data/supporting_files/Terminology.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lorenzorinaldi/Documents/GitHub/MARIO/doc/source/_static/data/supporting_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C34F573-4B2A-C444-A947-5D592C28D65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0774540-8828-1541-9D53-BED721D08A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26880" activeTab="4" xr2:uid="{191C6CC1-D0C2-3B4B-A0D5-6A4A3794157A}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26880" activeTab="2" xr2:uid="{191C6CC1-D0C2-3B4B-A0D5-6A4A3794157A}"/>
   </bookViews>
   <sheets>
     <sheet name="Matrices" sheetId="1" r:id="rId1"/>

--- a/doc/source/_static/data/supporting_files/Terminology.xlsx
+++ b/doc/source/_static/data/supporting_files/Terminology.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lorenzorinaldi/Documents/GitHub/MARIO/doc/source/_static/data/supporting_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0774540-8828-1541-9D53-BED721D08A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878D9818-DF8A-F74C-93B0-71F1559B842D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26880" activeTab="2" xr2:uid="{191C6CC1-D0C2-3B4B-A0D5-6A4A3794157A}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17660" activeTab="3" xr2:uid="{191C6CC1-D0C2-3B4B-A0D5-6A4A3794157A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Matrices" sheetId="1" r:id="rId1"/>
+    <sheet name="Matrices" sheetId="6" r:id="rId1"/>
     <sheet name="Indices" sheetId="2" r:id="rId2"/>
     <sheet name="IOT" sheetId="3" r:id="rId3"/>
     <sheet name="SUT_IT" sheetId="4" r:id="rId4"/>
     <sheet name="SUT_PT" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Matrices!$A$1:$G$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Matrices!$A$1:$G$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="205">
   <si>
     <t>Also known as</t>
   </si>
@@ -226,9 +226,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Total (direct+indirect) environmental transaction coefficients matrix</t>
-  </si>
-  <si>
     <t>D_cba, con</t>
   </si>
   <si>
@@ -394,12 +391,6 @@
     <t>Total (direct+indirect) environmental transaction flows by actvity matrix</t>
   </si>
   <si>
-    <t>Total (direct+indirect) environmental transaction coefficients by commodity matrix</t>
-  </si>
-  <si>
-    <t>Total (direct+indirect) environmental transaction coefficients by activity matrix</t>
-  </si>
-  <si>
     <t>wcc</t>
   </si>
   <si>
@@ -529,12 +520,6 @@
     <t>bs</t>
   </si>
   <si>
-    <t>Use transaction direct-output coefficients matrix</t>
-  </si>
-  <si>
-    <t>Supply transaction direct-output coefficients matrix</t>
-  </si>
-  <si>
     <t>gcc</t>
   </si>
   <si>
@@ -547,18 +532,6 @@
     <t>gaa</t>
   </si>
   <si>
-    <t>Ghosh inverse matrix, commodity-by-commodity coefficients</t>
-  </si>
-  <si>
-    <t>Ghosh inverse matrix, commodity-by-activity coefficients</t>
-  </si>
-  <si>
-    <t>Ghosh inverse matrix, activity-by-commodity coefficients</t>
-  </si>
-  <si>
-    <t>Ghosh inverse matrix, activity-by-activity coefficients</t>
-  </si>
-  <si>
     <t>mc_ex</t>
   </si>
   <si>
@@ -680,6 +653,33 @@
   </si>
   <si>
     <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>Total (direct+indirect) environmental coefficients matrix</t>
+  </si>
+  <si>
+    <t>p_ex</t>
+  </si>
+  <si>
+    <t>Price index, exploded by origin region and sector</t>
+  </si>
+  <si>
+    <t>Total (direct+indirect) environmental coefficients by commodity matrix</t>
+  </si>
+  <si>
+    <t>Total (direct+indirect) environmental coefficients by activity matrix</t>
+  </si>
+  <si>
+    <t>pc_ex</t>
+  </si>
+  <si>
+    <t>Price indices by commodity, exploded by origin region and activity</t>
+  </si>
+  <si>
+    <t>pa_ex</t>
+  </si>
+  <si>
+    <t>Price indices by activity, exploded by origin region and activity</t>
   </si>
 </sst>
 </file>
@@ -886,7 +886,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -1028,14 +1028,9 @@
     <xf numFmtId="165" fontId="2" fillId="15" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1370,16 +1365,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15D6DF91-CF4F-D845-84FA-5FC099A8086B}">
-  <dimension ref="A1:G62"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23C71EC4-6295-F64F-BCA2-2EFBB7B91189}">
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
     <col min="2" max="2" width="15.33203125" customWidth="1"/>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="70.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="88.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1535,7 +1530,7 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F7" t="s">
         <v>46</v>
@@ -1575,7 +1570,7 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
         <v>39</v>
@@ -1644,7 +1639,7 @@
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
         <v>39</v>
@@ -1701,7 +1696,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -1710,10 +1705,10 @@
         <v>8</v>
       </c>
       <c r="E15" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="F15" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="G15" t="s">
         <v>7</v>
@@ -1730,7 +1725,7 @@
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E16" t="s">
         <v>51</v>
@@ -1756,7 +1751,7 @@
         <v>44</v>
       </c>
       <c r="E17" t="s">
-        <v>53</v>
+        <v>196</v>
       </c>
       <c r="F17" t="s">
         <v>47</v>
@@ -1767,7 +1762,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
@@ -1776,10 +1771,10 @@
         <v>8</v>
       </c>
       <c r="E18" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F18" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="G18" t="s">
         <v>7</v>
@@ -1787,7 +1782,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
@@ -1796,7 +1791,7 @@
         <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F19" t="s">
         <v>7</v>
@@ -1807,68 +1802,65 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>60</v>
+        <v>198</v>
       </c>
       <c r="F20" t="s">
-        <v>61</v>
+        <v>167</v>
       </c>
       <c r="G20" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" t="s">
         <v>61</v>
-      </c>
-      <c r="G21" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G22" t="s">
         <v>61</v>
@@ -1876,30 +1868,30 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="E23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1907,19 +1899,22 @@
       <c r="C24" t="s">
         <v>9</v>
       </c>
+      <c r="D24" t="s">
+        <v>15</v>
+      </c>
       <c r="E24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F24" t="s">
         <v>61</v>
       </c>
       <c r="G24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -1927,14 +1922,11 @@
       <c r="C25" t="s">
         <v>9</v>
       </c>
-      <c r="D25" t="s">
-        <v>16</v>
-      </c>
       <c r="E25" t="s">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="F25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G25" t="s">
         <v>61</v>
@@ -1942,7 +1934,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
@@ -1954,18 +1946,18 @@
         <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G26" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
@@ -1977,10 +1969,10 @@
         <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F27" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G27" t="s">
         <v>61</v>
@@ -1988,7 +1980,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
@@ -2000,41 +1992,41 @@
         <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="F29" t="s">
         <v>61</v>
       </c>
       <c r="G29" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
@@ -2046,10 +2038,10 @@
         <v>21</v>
       </c>
       <c r="E30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F30" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G30" t="s">
         <v>23</v>
@@ -2057,7 +2049,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
@@ -2066,21 +2058,21 @@
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F31" t="s">
         <v>61</v>
       </c>
       <c r="G31" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
@@ -2089,13 +2081,13 @@
         <v>9</v>
       </c>
       <c r="D32" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="E32" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F32" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G32" t="s">
         <v>41</v>
@@ -2103,7 +2095,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
@@ -2111,14 +2103,17 @@
       <c r="C33" t="s">
         <v>9</v>
       </c>
+      <c r="D33" t="s">
+        <v>24</v>
+      </c>
       <c r="E33" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F33" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G33" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
@@ -2138,21 +2133,21 @@
         <v>46</v>
       </c>
       <c r="G34" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F35" t="s">
         <v>46</v>
@@ -2163,7 +2158,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
@@ -2172,30 +2167,30 @@
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F36" t="s">
         <v>46</v>
       </c>
       <c r="G36" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G37" t="s">
         <v>61</v>
@@ -2203,7 +2198,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
@@ -2212,27 +2207,27 @@
         <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F38" t="s">
         <v>47</v>
       </c>
       <c r="G38" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
         <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F39" t="s">
         <v>47</v>
@@ -2243,7 +2238,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
         <v>14</v>
@@ -2252,30 +2247,30 @@
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F40" t="s">
         <v>47</v>
       </c>
       <c r="G40" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C41" t="s">
         <v>9</v>
       </c>
       <c r="E41" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="F41" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G41" t="s">
         <v>61</v>
@@ -2292,27 +2287,27 @@
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F42" t="s">
         <v>46</v>
       </c>
       <c r="G42" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C43" t="s">
         <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F43" t="s">
         <v>46</v>
@@ -2323,7 +2318,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
@@ -2332,18 +2327,18 @@
         <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F44" t="s">
         <v>46</v>
       </c>
       <c r="G44" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>164</v>
+        <v>97</v>
       </c>
       <c r="B45" t="s">
         <v>14</v>
@@ -2352,10 +2347,10 @@
         <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="F45" t="s">
-        <v>166</v>
+        <v>46</v>
       </c>
       <c r="G45" t="s">
         <v>61</v>
@@ -2363,39 +2358,39 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
       </c>
       <c r="C46" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E46" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="F46" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="G46" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>100</v>
+        <v>158</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C47" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E47" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="F47" t="s">
-        <v>47</v>
+        <v>157</v>
       </c>
       <c r="G47" t="s">
         <v>61</v>
@@ -2412,27 +2407,27 @@
         <v>9</v>
       </c>
       <c r="E48" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F48" t="s">
         <v>47</v>
       </c>
       <c r="G48" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C49" t="s">
         <v>9</v>
       </c>
       <c r="E49" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F49" t="s">
         <v>47</v>
@@ -2443,7 +2438,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
@@ -2452,18 +2447,18 @@
         <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>110</v>
+        <v>199</v>
       </c>
       <c r="F50" t="s">
         <v>47</v>
       </c>
       <c r="G50" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>169</v>
+        <v>101</v>
       </c>
       <c r="B51" t="s">
         <v>14</v>
@@ -2472,10 +2467,10 @@
         <v>9</v>
       </c>
       <c r="E51" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="F51" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="G51" t="s">
         <v>61</v>
@@ -2483,47 +2478,47 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="B52" t="s">
         <v>14</v>
       </c>
       <c r="C52" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E52" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="F52" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="G52" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="B53" t="s">
         <v>14</v>
       </c>
       <c r="C53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E53" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="F53" t="s">
+        <v>162</v>
+      </c>
+      <c r="G53" t="s">
         <v>61</v>
       </c>
-      <c r="G53" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B54" t="s">
         <v>14</v>
@@ -2532,10 +2527,10 @@
         <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F54" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G54" t="s">
         <v>41</v>
@@ -2549,24 +2544,21 @@
         <v>14</v>
       </c>
       <c r="C55" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" t="s">
-        <v>123</v>
+        <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F55" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="G55" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>119</v>
+        <v>201</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
@@ -2574,159 +2566,84 @@
       <c r="C56" t="s">
         <v>8</v>
       </c>
-      <c r="D56" t="s">
-        <v>120</v>
-      </c>
       <c r="E56" t="s">
-        <v>121</v>
+        <v>202</v>
       </c>
       <c r="F56" t="s">
-        <v>7</v>
+        <v>157</v>
       </c>
       <c r="G56" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>152</v>
+        <v>203</v>
       </c>
       <c r="B57" t="s">
         <v>14</v>
       </c>
       <c r="C57" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" t="s">
-        <v>123</v>
+        <v>8</v>
       </c>
       <c r="E57" t="s">
-        <v>154</v>
+        <v>204</v>
       </c>
       <c r="F57" t="s">
+        <v>157</v>
+      </c>
+      <c r="G57" t="s">
         <v>61</v>
-      </c>
-      <c r="G57" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>153</v>
+        <v>116</v>
       </c>
       <c r="B58" t="s">
         <v>14</v>
       </c>
       <c r="C58" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E58" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="F58" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="G58" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="B59" t="s">
         <v>14</v>
       </c>
       <c r="C59" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D59" t="s">
         <v>120</v>
       </c>
       <c r="E59" t="s">
-        <v>160</v>
+        <v>119</v>
       </c>
       <c r="F59" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="G59" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>157</v>
-      </c>
-      <c r="B60" t="s">
-        <v>14</v>
-      </c>
-      <c r="C60" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" t="s">
-        <v>120</v>
-      </c>
-      <c r="E60" t="s">
-        <v>161</v>
-      </c>
-      <c r="F60" t="s">
-        <v>61</v>
-      </c>
-      <c r="G60" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>158</v>
-      </c>
-      <c r="B61" t="s">
-        <v>14</v>
-      </c>
-      <c r="C61" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" t="s">
-        <v>120</v>
-      </c>
-      <c r="E61" t="s">
-        <v>162</v>
-      </c>
-      <c r="F61" t="s">
-        <v>62</v>
-      </c>
-      <c r="G61" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>159</v>
-      </c>
-      <c r="B62" t="s">
-        <v>14</v>
-      </c>
-      <c r="C62" t="s">
-        <v>9</v>
-      </c>
-      <c r="D62" t="s">
-        <v>120</v>
-      </c>
-      <c r="E62" t="s">
-        <v>163</v>
-      </c>
-      <c r="F62" t="s">
-        <v>62</v>
-      </c>
-      <c r="G62" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G62" xr:uid="{15D6DF91-CF4F-D845-84FA-5FC099A8086B}"/>
+  <autoFilter ref="A1:G12" xr:uid="{15D6DF91-CF4F-D845-84FA-5FC099A8086B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2745,13 +2662,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>52</v>
@@ -2761,72 +2678,72 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -2834,13 +2751,13 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -2848,13 +2765,13 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -2888,7 +2805,7 @@
   <sheetData>
     <row r="1" spans="1:18" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2896,63 +2813,63 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="H1" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="H2" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:18" s="5" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -2963,7 +2880,7 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -2974,14 +2891,14 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="F5" s="4"/>
       <c r="O5" s="3" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:18" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -2991,7 +2908,7 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
@@ -3025,13 +2942,13 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="7">
@@ -3066,13 +2983,13 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="7">
@@ -3107,13 +3024,13 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="7">
@@ -3148,13 +3065,13 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="7">
@@ -3189,13 +3106,13 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="7">
@@ -3230,13 +3147,13 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="12">
@@ -3301,10 +3218,10 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C17" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="19">
@@ -3335,10 +3252,10 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C18" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="19">
@@ -3369,10 +3286,10 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C19" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="22">
@@ -3430,10 +3347,10 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D22" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="27">
@@ -3464,10 +3381,10 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D23" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="30">
@@ -3503,13 +3420,13 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H26" s="34" cm="1">
         <f t="array" ref="H26:M31">MMULT(H9:M14,MINVERSE(_xlfn.MUNIT(6)*R9:R14))</f>
@@ -3533,13 +3450,13 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H27" s="34">
         <v>0.18988705204672909</v>
@@ -3562,13 +3479,13 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H28" s="34">
         <v>0.11255289603718815</v>
@@ -3591,13 +3508,13 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H29" s="34">
         <v>4.1802211373763623E-5</v>
@@ -3620,13 +3537,13 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H30" s="34">
         <v>1.5945275639065704E-4</v>
@@ -3649,13 +3566,13 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H31" s="34">
         <v>6.9102184929874483E-4</v>
@@ -3681,18 +3598,18 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="H33" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H34" s="34" cm="1">
         <f t="array" ref="H34:M39">MMULT(MINVERSE(_xlfn.MUNIT(6)*R9:R14),H9:M14)</f>
@@ -3716,13 +3633,13 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H35" s="34">
         <v>1.8121276769731104E-2</v>
@@ -3745,13 +3662,13 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H36" s="34">
         <v>2.1131241027855317E-2</v>
@@ -3774,13 +3691,13 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H37" s="34">
         <v>5.220544786203314E-3</v>
@@ -3803,13 +3720,13 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H38" s="34">
         <v>6.5742534403949524E-4</v>
@@ -3832,13 +3749,13 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H39" s="34">
         <v>5.7632220193467804E-3</v>
@@ -3871,10 +3788,10 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C42" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H42" s="35" cm="1">
         <f t="array" ref="H42:M44">MMULT(H17:M19,MINVERSE(_xlfn.MUNIT(6)*R9:R14))</f>
@@ -3898,10 +3815,10 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C43" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H43" s="35">
         <v>0.25840155423314187</v>
@@ -3924,10 +3841,10 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C44" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H44" s="35">
         <v>0.28959395681537642</v>
@@ -3959,10 +3876,10 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D47" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="H47" s="36" cm="1">
         <f t="array" ref="H47:M48">MMULT(H22:M23,MINVERSE(_xlfn.MUNIT(6)*R9:R14))</f>
@@ -3986,10 +3903,10 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D48" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H48" s="36">
         <v>342552.27019182622</v>
@@ -4017,13 +3934,13 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H51" s="37" cm="1">
         <f t="array" ref="H51:M56">MINVERSE(_xlfn.MUNIT(6)-_xlfn.ANCHORARRAY(H26))</f>
@@ -4047,13 +3964,13 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H52" s="37">
         <v>0.38267380633193693</v>
@@ -4076,13 +3993,13 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H53" s="37">
         <v>0.29462466705105084</v>
@@ -4105,13 +4022,13 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H54" s="37">
         <v>1.3911529653568301E-4</v>
@@ -4134,13 +4051,13 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H55" s="37">
         <v>1.5501897732239519E-3</v>
@@ -4163,13 +4080,13 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H56" s="37">
         <v>2.4862356370802864E-3</v>
@@ -4192,18 +4109,18 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="H58" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H59" s="37" cm="1">
         <f t="array" ref="H59:M64">MINVERSE(_xlfn.MUNIT(6)-_xlfn.ANCHORARRAY(H34))</f>
@@ -4227,13 +4144,13 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H60" s="37">
         <v>3.65192775511676E-2</v>
@@ -4256,13 +4173,13 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H61" s="37">
         <v>5.5314301731963791E-2</v>
@@ -4285,13 +4202,13 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H62" s="37">
         <v>1.7373665462739368E-2</v>
@@ -4314,13 +4231,13 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H63" s="37">
         <v>6.3914482763245501E-3</v>
@@ -4343,13 +4260,13 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H64" s="37">
         <v>2.0735564271153945E-2</v>
@@ -4382,10 +4299,10 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C67" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H67" s="38" cm="1">
         <f t="array" ref="H67:M69">MMULT(_xlfn.ANCHORARRAY(H42),_xlfn.ANCHORARRAY(H51))</f>
@@ -4409,10 +4326,10 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C68" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H68" s="38">
         <v>0.45288217149840237</v>
@@ -4435,10 +4352,10 @@
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C69" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H69" s="38">
         <v>0.44860583416000482</v>
@@ -4465,12 +4382,12 @@
     <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="F71" s="6"/>
       <c r="H71" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="F72" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H72" s="39" cm="1">
         <f t="array" ref="H72:M72">MMULT({1,1,1},_xlfn.ANCHORARRAY(H67))</f>
@@ -4503,10 +4420,10 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D75" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="H75" s="40" cm="1">
         <f t="array" ref="H75:M76">MMULT(_xlfn.ANCHORARRAY(H47),_xlfn.ANCHORARRAY(H51))</f>
@@ -4530,10 +4447,10 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D76" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H76" s="40">
         <v>508912.51207678294</v>
@@ -4556,21 +4473,21 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="H78" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="F79" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H79" s="38" cm="1">
         <f t="array" ref="H79:M84">MMULT(_xlfn.MUNIT(6)*H42:M42,_xlfn.ANCHORARRAY(H51))</f>
@@ -4594,16 +4511,16 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H80" s="38">
         <v>1.8349756500161407E-2</v>
@@ -4626,16 +4543,16 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H81" s="38">
         <v>1.690183565561329E-2</v>
@@ -4658,16 +4575,16 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="F82" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H82" s="38">
         <v>8.5515160062883893E-6</v>
@@ -4690,16 +4607,16 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H83" s="38">
         <v>9.2177562337358287E-5</v>
@@ -4722,16 +4639,16 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H84" s="38">
         <v>7.6628966365200954E-5</v>
@@ -4754,16 +4671,16 @@
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H85" s="38" cm="1">
         <f t="array" ref="H85:M90">MMULT(_xlfn.MUNIT(6)*H43:M43,_xlfn.ANCHORARRAY(H51))</f>
@@ -4787,16 +4704,16 @@
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B86" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C86" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="F86" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H86" s="38">
         <v>0.12229545418529501</v>
@@ -4819,16 +4736,16 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H87" s="38">
         <v>3.501156810702883E-2</v>
@@ -4851,16 +4768,16 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H88" s="38">
         <v>1.6897558978936883E-5</v>
@@ -4883,16 +4800,16 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C89" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="F89" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H89" s="38">
         <v>4.8358910073498457E-4</v>
@@ -4915,16 +4832,16 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H90" s="38">
         <v>4.4343553969406803E-4</v>
@@ -4947,16 +4864,16 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H91" s="38" cm="1">
         <f t="array" ref="H91:M96">MMULT(_xlfn.MUNIT(6)*H44:M44,_xlfn.ANCHORARRAY(H51))</f>
@@ -4980,16 +4897,16 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H92" s="38">
         <v>8.664879349787738E-2</v>
@@ -5012,16 +4929,16 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B93" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C93" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="F93" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H93" s="38">
         <v>3.1154762357866083E-2</v>
@@ -5044,16 +4961,16 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H94" s="38">
         <v>5.3632484584051431E-5</v>
@@ -5076,16 +4993,16 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H95" s="38">
         <v>3.3963965305618701E-4</v>
@@ -5108,16 +5025,16 @@
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C96" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="F96" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H96" s="38">
         <v>2.1198748596574929E-4</v>
@@ -5140,21 +5057,21 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="H98" s="2" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="H99" s="40" cm="1">
         <f t="array" ref="H99:M104">MMULT(_xlfn.MUNIT(6)*H47:M47,_xlfn.ANCHORARRAY(H51))</f>
@@ -5178,16 +5095,16 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="H100" s="40">
         <v>7.5085674981095907E-3</v>
@@ -5210,16 +5127,16 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="H101" s="40">
         <v>3.6319298618620326E-3</v>
@@ -5242,16 +5159,16 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="H102" s="40">
         <v>1.2880587894550417E-6</v>
@@ -5274,16 +5191,16 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="H103" s="40">
         <v>1.1872879686569632E-5</v>
@@ -5306,16 +5223,16 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="H104" s="40">
         <v>8.1918503857684624E-6</v>
@@ -5338,16 +5255,16 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H105" s="40" cm="1">
         <f t="array" ref="H105:M110">MMULT(_xlfn.MUNIT(6)*H48:M48,_xlfn.ANCHORARRAY(H51))</f>
@@ -5371,16 +5288,16 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H106" s="40">
         <v>68801.608636738281</v>
@@ -5403,16 +5320,16 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H107" s="40">
         <v>49281.851288924401</v>
@@ -5435,16 +5352,16 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H108" s="40">
         <v>40.33821446868901</v>
@@ -5467,16 +5384,16 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H109" s="40">
         <v>107.63245737059442</v>
@@ -5499,16 +5416,16 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H110" s="40">
         <v>100.63013463608938</v>
@@ -5535,12 +5452,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C113" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="H113" s="41" cm="1">
         <f t="array" ref="H113:M115">MMULT(_xlfn.ANCHORARRAY(H67),MMULT(O9:P14,{1;1})*_xlfn.MUNIT(6))</f>
@@ -5562,12 +5479,12 @@
         <v>58221.726115639329</v>
       </c>
     </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C114" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="H114" s="41">
         <v>1152546.1393933955</v>
@@ -5588,12 +5505,12 @@
         <v>285484.84872343595</v>
       </c>
     </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C115" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="H115" s="41">
         <v>1141663.2290023617</v>
@@ -5614,22 +5531,22 @@
         <v>187843.29905448397</v>
       </c>
     </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="F116" s="6"/>
       <c r="G116" s="6"/>
     </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="F117" s="6"/>
       <c r="H117" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D118" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="H118" s="42" cm="1">
         <f t="array" ref="H118:M119">MMULT(_xlfn.ANCHORARRAY(H75),MMULT(O9:P14,{1;1})*_xlfn.MUNIT(6))</f>
@@ -5651,12 +5568,12 @@
         <v>18537.507598199572</v>
       </c>
     </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D119" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="H119" s="42">
         <v>1295138532705.8743</v>
@@ -5677,21 +5594,16 @@
         <v>121392266458.77629</v>
       </c>
     </row>
-    <row r="120" spans="1:23" s="49" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="F120" s="50"/>
-      <c r="H120" s="51"/>
-      <c r="I120" s="51"/>
-      <c r="J120" s="51"/>
-      <c r="K120" s="51"/>
-      <c r="L120" s="51"/>
-      <c r="M120" s="51"/>
-      <c r="S120" s="52"/>
-      <c r="T120" s="52"/>
-      <c r="U120" s="52"/>
-      <c r="V120" s="52"/>
-      <c r="W120" s="52"/>
-    </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="F120" s="6"/>
+      <c r="H120" s="49"/>
+      <c r="I120" s="49"/>
+      <c r="J120" s="49"/>
+      <c r="K120" s="49"/>
+      <c r="L120" s="49"/>
+      <c r="M120" s="49"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="H121" s="2" t="s">
         <v>3</v>
       </c>
@@ -5701,15 +5613,15 @@
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
     </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G122" s="6"/>
       <c r="H122" s="7" cm="1">
@@ -5732,15 +5644,15 @@
         <v>50607.806861405676</v>
       </c>
     </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G123" s="6"/>
       <c r="H123" s="7">
@@ -5762,15 +5674,15 @@
         <v>27813.857216071825</v>
       </c>
     </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G124" s="6"/>
       <c r="H124" s="7">
@@ -5792,15 +5704,15 @@
         <v>134910.65754329169</v>
       </c>
     </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G125" s="6"/>
       <c r="H125" s="7">
@@ -5822,15 +5734,15 @@
         <v>30635.045695900892</v>
       </c>
     </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G126" s="6"/>
       <c r="H126" s="7">
@@ -5852,15 +5764,15 @@
         <v>312355.77524189529</v>
       </c>
     </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G127" s="6"/>
       <c r="H127" s="12">
@@ -5882,7 +5794,7 @@
         <v>287300.67335464072</v>
       </c>
     </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="F128" s="6"/>
       <c r="G128" s="6"/>
       <c r="H128" s="9"/>
@@ -5906,10 +5818,10 @@
     </row>
     <row r="130" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C130" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G130" s="6"/>
       <c r="H130" s="19" cm="1">
@@ -5934,10 +5846,10 @@
     </row>
     <row r="131" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C131" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G131" s="6"/>
       <c r="H131" s="19">
@@ -5961,10 +5873,10 @@
     </row>
     <row r="132" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C132" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G132" s="6"/>
       <c r="H132" s="22">
@@ -6010,10 +5922,10 @@
     </row>
     <row r="135" spans="3:13" x14ac:dyDescent="0.2">
       <c r="D135" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G135" s="6"/>
       <c r="H135" s="27" cm="1">
@@ -6038,10 +5950,10 @@
     </row>
     <row r="136" spans="3:13" x14ac:dyDescent="0.2">
       <c r="D136" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="G136" s="6"/>
       <c r="H136" s="30">
@@ -6093,7 +6005,7 @@
   <sheetData>
     <row r="1" spans="1:22" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6102,40 +6014,40 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="I1" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -6143,16 +6055,16 @@
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="I2" s="5" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
@@ -6164,7 +6076,7 @@
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -6176,16 +6088,16 @@
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="5" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:22" s="5" customFormat="1" ht="32" x14ac:dyDescent="0.2">
@@ -6193,7 +6105,7 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -6205,7 +6117,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
@@ -6217,14 +6129,14 @@
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="G6" s="4"/>
       <c r="S6" s="5" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:22" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -6235,29 +6147,29 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="N8" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -6290,13 +6202,13 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -6329,13 +6241,13 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -6368,13 +6280,13 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -6422,7 +6334,7 @@
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="G14" s="6"/>
       <c r="I14" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -6433,23 +6345,21 @@
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
-      <c r="S14" s="2" t="s">
-        <v>69</v>
-      </c>
+      <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="V14" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I15" s="43">
         <v>1240653451807.9199</v>
@@ -6469,12 +6379,8 @@
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
-      <c r="S15" s="10">
-        <v>0</v>
-      </c>
-      <c r="T15" s="10">
-        <v>0</v>
-      </c>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
       <c r="V15" s="45">
         <f>SUM(I15:L15,S15:T15)</f>
         <v>1275532677156.157</v>
@@ -6482,13 +6388,13 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I16" s="43">
         <v>70776495966.181396</v>
@@ -6508,12 +6414,8 @@
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
-      <c r="S16" s="10">
-        <v>0</v>
-      </c>
-      <c r="T16" s="10">
-        <v>0</v>
-      </c>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
       <c r="V16" s="45">
         <f>SUM(I16:L16,S16:T16)</f>
         <v>2418662221999.3018</v>
@@ -6521,13 +6423,13 @@
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I17" s="7">
         <v>0</v>
@@ -6547,12 +6449,8 @@
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
-      <c r="S17" s="10">
-        <v>0</v>
-      </c>
-      <c r="T17" s="10">
-        <v>0</v>
-      </c>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
       <c r="V17" s="45">
         <f>SUM(I17:L17,S17:T17)</f>
         <v>63087672571000.289</v>
@@ -6560,13 +6458,13 @@
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I18" s="7">
         <v>0</v>
@@ -6586,12 +6484,8 @@
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
-      <c r="S18" s="10">
-        <v>0</v>
-      </c>
-      <c r="T18" s="10">
-        <v>0</v>
-      </c>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
       <c r="V18" s="45">
         <f>SUM(I18:L18,S18:T18)</f>
         <v>104495163828835.61</v>
@@ -6615,14 +6509,14 @@
     <row r="20" spans="1:22" x14ac:dyDescent="0.2">
       <c r="G20" s="6"/>
       <c r="I20" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -6635,10 +6529,10 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D21" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I21" s="46">
         <v>0</v>
@@ -6675,10 +6569,10 @@
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D22" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I22" s="46">
         <v>0</v>
@@ -6715,10 +6609,10 @@
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D23" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I23" s="46">
         <v>0</v>
@@ -6771,14 +6665,14 @@
     <row r="25" spans="1:22" x14ac:dyDescent="0.2">
       <c r="G25" s="6"/>
       <c r="I25" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -6791,10 +6685,10 @@
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.2">
       <c r="E26" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="I26" s="47">
         <v>0</v>
@@ -6831,10 +6725,10 @@
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="E27" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I27" s="47">
         <v>0</v>
@@ -6890,7 +6784,7 @@
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -6901,13 +6795,13 @@
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
@@ -6933,13 +6827,13 @@
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
@@ -6964,13 +6858,13 @@
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
@@ -6995,13 +6889,13 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
@@ -7046,7 +6940,7 @@
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -7057,13 +6951,13 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
@@ -7089,13 +6983,13 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
@@ -7120,13 +7014,13 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
@@ -7151,13 +7045,13 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
@@ -7198,7 +7092,7 @@
     <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G41" s="6"/>
       <c r="I41" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -7214,13 +7108,13 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I42" s="34" cm="1">
         <f t="array" ref="I42:L45">MMULT(I15:L18,MINVERSE(_xlfn.MUNIT(4)*V9:V12))</f>
@@ -7246,13 +7140,13 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I43" s="34">
         <v>5.3968948978525721E-2</v>
@@ -7277,13 +7171,13 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I44" s="34">
         <v>0</v>
@@ -7308,13 +7202,13 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I45" s="34">
         <v>0</v>
@@ -7354,7 +7248,7 @@
     <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G47" s="6"/>
       <c r="I47" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
@@ -7369,13 +7263,13 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I48" s="34" cm="1">
         <f t="array" ref="I48:L51">MMULT(MINVERSE(_xlfn.MUNIT(4)*V15:V18),I15:L18)</f>
@@ -7400,13 +7294,13 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I49" s="34">
         <v>2.9262662360383874E-2</v>
@@ -7430,13 +7324,13 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I50" s="34">
         <v>0</v>
@@ -7460,13 +7354,13 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I51" s="34">
         <v>0</v>
@@ -7505,14 +7399,14 @@
     <row r="53" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G53" s="6"/>
       <c r="I53" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
       <c r="N53" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" s="2"/>
@@ -7523,10 +7417,10 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D54" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I54" s="35" cm="1">
         <f t="array" ref="I54:L56">MMULT(I21:L23,MINVERSE(_xlfn.MUNIT(4)*V9:V12))</f>
@@ -7561,10 +7455,10 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D55" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I55" s="35">
         <v>0</v>
@@ -7597,10 +7491,10 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D56" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I56" s="35">
         <v>0</v>
@@ -7649,14 +7543,14 @@
     <row r="58" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G58" s="6"/>
       <c r="I58" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
       <c r="N58" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" s="2"/>
@@ -7667,10 +7561,10 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E59" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="I59" s="36" cm="1">
         <f t="array" ref="I59:L60">MMULT(I26:L27,MINVERSE(_xlfn.MUNIT(4)*V9:V12))</f>
@@ -7705,10 +7599,10 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E60" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="I60" s="36">
         <v>0</v>
@@ -7755,14 +7649,14 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.2">
       <c r="I62" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
       <c r="N62" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
@@ -7773,13 +7667,13 @@
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I63" s="37" cm="1">
         <f t="array" ref="I63:L66">MINVERSE(_xlfn.MUNIT(4)-MMULT(N30:Q33,I42:L45))</f>
@@ -7814,13 +7708,13 @@
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I64" s="37">
         <v>0.51048045676514109</v>
@@ -7853,13 +7747,13 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I65" s="37">
         <v>0.43670060841534108</v>
@@ -7892,13 +7786,13 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I66" s="37">
         <v>0.17175775744316804</v>
@@ -7947,14 +7841,14 @@
     <row r="68" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G68" s="6"/>
       <c r="I68" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
       <c r="N68" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" s="2"/>
@@ -7965,13 +7859,13 @@
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I69" s="37" cm="1">
         <f t="array" ref="I69:L72">MMULT(_xlfn.ANCHORARRAY(N69),_xlfn.ANCHORARRAY(I42))</f>
@@ -8006,13 +7900,13 @@
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I70" s="37">
         <v>0.57777365343221754</v>
@@ -8045,13 +7939,13 @@
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I71" s="37">
         <v>0.43367610171134424</v>
@@ -8084,13 +7978,13 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I72" s="37">
         <v>0.1747822641277908</v>
@@ -8137,14 +8031,14 @@
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.2">
       <c r="I74" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
       <c r="N74" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" s="2"/>
@@ -8155,13 +8049,13 @@
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I75" s="37" cm="1">
         <f t="array" ref="I75:L78">MINVERSE(_xlfn.MUNIT(4)-MMULT(N36:Q39,_xlfn.ANCHORARRAY(I48)))</f>
@@ -8196,13 +8090,13 @@
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I76" s="37">
         <v>0.28095904241499059</v>
@@ -8235,13 +8129,13 @@
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I77" s="37">
         <v>9.0865064104290842E-3</v>
@@ -8274,13 +8168,13 @@
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I78" s="37">
         <v>2.1543506163039516E-3</v>
@@ -8329,14 +8223,14 @@
     <row r="80" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G80" s="6"/>
       <c r="I80" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
       <c r="N80" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" s="2"/>
@@ -8347,13 +8241,13 @@
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I81" s="37" cm="1">
         <f t="array" ref="I81:L84">MMULT(_xlfn.ANCHORARRAY(N81),_xlfn.ANCHORARRAY(I48))</f>
@@ -8388,13 +8282,13 @@
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I82" s="37">
         <v>0.31327634984775804</v>
@@ -8427,13 +8321,13 @@
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I83" s="37">
         <v>9.015007281903447E-3</v>
@@ -8466,13 +8360,13 @@
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I84" s="37">
         <v>2.1935435784963429E-3</v>
@@ -8520,14 +8414,14 @@
     <row r="86" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G86" s="6"/>
       <c r="I86" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
       <c r="N86" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" s="2"/>
@@ -8538,10 +8432,10 @@
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D87" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I87" s="38" cm="1">
         <f t="array" ref="I87:L89">MMULT(MMULT(_xlfn.ANCHORARRAY(N54),_xlfn.ANCHORARRAY(I42))+_xlfn.ANCHORARRAY(I54),_xlfn.ANCHORARRAY(I63))</f>
@@ -8576,10 +8470,10 @@
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D88" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I88" s="38">
         <v>0.57084102204055065</v>
@@ -8612,10 +8506,10 @@
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D89" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I89" s="38">
         <v>0.3617831968879418</v>
@@ -8664,14 +8558,14 @@
     <row r="91" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G91" s="6"/>
       <c r="I91" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
       <c r="N91" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
@@ -8682,7 +8576,7 @@
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G92" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I92" s="39" cm="1">
         <f t="array" ref="I92:L92">MMULT({1,1,1},_xlfn.ANCHORARRAY(I87))</f>
@@ -8732,14 +8626,14 @@
     <row r="94" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G94" s="6"/>
       <c r="I94" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
       <c r="N94" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" s="2"/>
@@ -8750,10 +8644,10 @@
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E95" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="I95" s="40" cm="1">
         <f t="array" ref="I95:L96">MMULT(MMULT(_xlfn.ANCHORARRAY(N59),_xlfn.ANCHORARRAY(I42))+_xlfn.ANCHORARRAY(I59),_xlfn.ANCHORARRAY(I63))</f>
@@ -8788,10 +8682,10 @@
     </row>
     <row r="96" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E96" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="I96" s="40">
         <v>25.067285417963596</v>
@@ -8839,14 +8733,14 @@
     <row r="98" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G98" s="6"/>
       <c r="I98" s="2" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
       <c r="N98" s="2" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" s="2"/>
@@ -8857,16 +8751,16 @@
     </row>
     <row r="99" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I99" s="38" cm="1">
         <f t="array" ref="I99:L102">MMULT(_xlfn.MUNIT(4)*N54:Q54,MMULT(_xlfn.ANCHORARRAY(I42),_xlfn.ANCHORARRAY(I63)))</f>
@@ -8901,16 +8795,16 @@
     </row>
     <row r="100" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I100" s="38">
         <v>1.1532599069206862E-2</v>
@@ -8943,16 +8837,16 @@
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I101" s="38">
         <v>2.037142347232819E-2</v>
@@ -8985,16 +8879,16 @@
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I102" s="38">
         <v>4.5204976370494896E-3</v>
@@ -9027,16 +8921,16 @@
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G103" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I103" s="38" cm="1">
         <f t="array" ref="I103:L106">MMULT(_xlfn.MUNIT(4)*N55:Q55,MMULT(_xlfn.ANCHORARRAY(I42),_xlfn.ANCHORARRAY(I63)))</f>
@@ -9071,16 +8965,16 @@
     </row>
     <row r="104" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C104" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D104" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D104" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="G104" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I104" s="38">
         <v>0.20306229387844224</v>
@@ -9113,16 +9007,16 @@
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I105" s="38">
         <v>6.5470551620854855E-2</v>
@@ -9155,16 +9049,16 @@
     </row>
     <row r="106" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C106" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D106" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D106" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="G106" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I106" s="38">
         <v>5.9717733343340691E-2</v>
@@ -9197,16 +9091,16 @@
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I107" s="38" cm="1">
         <f t="array" ref="I107:L110">MMULT(_xlfn.MUNIT(4)*N56:Q56,MMULT(_xlfn.ANCHORARRAY(I42),_xlfn.ANCHORARRAY(I63)))</f>
@@ -9241,16 +9135,16 @@
     </row>
     <row r="108" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I108" s="38">
         <v>0.12658762596537773</v>
@@ -9283,16 +9177,16 @@
     </row>
     <row r="109" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I109" s="38">
         <v>5.846161664714588E-2</v>
@@ -9325,16 +9219,16 @@
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I110" s="38">
         <v>3.9575931407557552E-2</v>
@@ -9382,14 +9276,14 @@
     <row r="112" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G112" s="6"/>
       <c r="I112" s="2" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="J112" s="2"/>
       <c r="K112" s="2"/>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
       <c r="N112" s="2" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" s="2"/>
@@ -9400,16 +9294,16 @@
     </row>
     <row r="113" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I113" s="40" cm="1">
         <f t="array" ref="I113:L116">MMULT(_xlfn.MUNIT(4)*N59:Q59,MMULT(_xlfn.ANCHORARRAY(I42),_xlfn.ANCHORARRAY(I63)))</f>
@@ -9444,16 +9338,16 @@
     </row>
     <row r="114" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I114" s="40">
         <v>1.5641275438919316E-7</v>
@@ -9486,16 +9380,16 @@
     </row>
     <row r="115" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I115" s="40">
         <v>1.3242298681587328E-10</v>
@@ -9528,16 +9422,16 @@
     </row>
     <row r="116" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I116" s="40">
         <v>6.5895681790486286E-12</v>
@@ -9570,16 +9464,16 @@
     </row>
     <row r="117" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I117" s="48" cm="1">
         <f t="array" ref="I117:L120">MMULT(_xlfn.MUNIT(4)*N60:Q60,MMULT(_xlfn.ANCHORARRAY(I42),_xlfn.ANCHORARRAY(I63)))</f>
@@ -9614,16 +9508,16 @@
     </row>
     <row r="118" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C118" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D118" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D118" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="G118" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I118" s="48">
         <v>2.122373061892596</v>
@@ -9656,16 +9550,16 @@
     </row>
     <row r="119" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I119" s="48">
         <v>1.3135561152989488E-3</v>
@@ -9698,16 +9592,16 @@
     </row>
     <row r="120" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C120" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D120" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D120" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="G120" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I120" s="48">
         <v>8.0947417472780015E-5</v>
@@ -9755,14 +9649,14 @@
     <row r="122" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G122" s="6"/>
       <c r="I122" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J122" s="2"/>
       <c r="K122" s="2"/>
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
       <c r="N122" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" s="2"/>
@@ -9772,10 +9666,10 @@
     </row>
     <row r="123" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D123" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G123" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I123" s="41" cm="1">
         <f t="array" ref="I123:L125">MMULT(_xlfn.ANCHORARRAY(I87),_xlfn.MUNIT(4)*MMULT(S9:T12,{1;1}))</f>
@@ -9809,10 +9703,10 @@
     </row>
     <row r="124" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D124" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I124" s="41">
         <v>339316087553.87622</v>
@@ -9844,10 +9738,10 @@
     </row>
     <row r="125" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D125" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G125" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I125" s="41">
         <v>215049119055.83008</v>
@@ -9895,14 +9789,14 @@
     <row r="127" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G127" s="6"/>
       <c r="I127" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J127" s="2"/>
       <c r="K127" s="2"/>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
       <c r="N127" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" s="2"/>
@@ -9913,10 +9807,10 @@
     </row>
     <row r="128" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D128" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="I128" s="42" cm="1">
         <f t="array" ref="I128:L129">MMULT(_xlfn.ANCHORARRAY(I95),_xlfn.MUNIT(4)*MMULT(S9:T12,{1;1}))</f>
@@ -9951,10 +9845,10 @@
     </row>
     <row r="129" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D129" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="I129" s="42">
         <v>14900353837947.408</v>
@@ -9987,18 +9881,18 @@
     </row>
     <row r="131" spans="1:20" x14ac:dyDescent="0.2">
       <c r="N131" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="132" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I132" s="2"/>
       <c r="J132" s="2"/>
@@ -10021,13 +9915,13 @@
     </row>
     <row r="133" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G133" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I133" s="2"/>
       <c r="J133" s="2"/>
@@ -10049,13 +9943,13 @@
     </row>
     <row r="134" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I134" s="2"/>
       <c r="J134" s="2"/>
@@ -10077,13 +9971,13 @@
     </row>
     <row r="135" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G135" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I135" s="2"/>
       <c r="J135" s="2"/>
@@ -10117,7 +10011,7 @@
     <row r="137" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G137" s="6"/>
       <c r="I137" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J137" s="2"/>
       <c r="K137" s="2"/>
@@ -10130,13 +10024,13 @@
     </row>
     <row r="138" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I138" s="43" cm="1">
         <f t="array" ref="I138:L141">MMULT(_xlfn.ANCHORARRAY(I42),_xlfn.MUNIT(4)*V9:V12)</f>
@@ -10159,13 +10053,13 @@
     </row>
     <row r="139" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G139" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I139" s="43">
         <v>70776495966.181396</v>
@@ -10187,13 +10081,13 @@
     </row>
     <row r="140" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I140" s="7">
         <v>0</v>
@@ -10215,13 +10109,13 @@
     </row>
     <row r="141" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G141" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I141" s="7">
         <v>0</v>
@@ -10256,14 +10150,14 @@
     <row r="143" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G143" s="6"/>
       <c r="I143" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J143" s="2"/>
       <c r="K143" s="2"/>
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
       <c r="N143" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" s="2"/>
@@ -10271,10 +10165,10 @@
     </row>
     <row r="144" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D144" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I144" s="46" cm="1">
         <f t="array" ref="I144:L146">MMULT(_xlfn.ANCHORARRAY(I54),_xlfn.MUNIT(4)*V9:V12)</f>
@@ -10306,10 +10200,10 @@
     </row>
     <row r="145" spans="4:17" x14ac:dyDescent="0.2">
       <c r="D145" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G145" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I145" s="46">
         <v>0</v>
@@ -10339,10 +10233,10 @@
     </row>
     <row r="146" spans="4:17" x14ac:dyDescent="0.2">
       <c r="D146" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I146" s="46">
         <v>0</v>
@@ -10385,14 +10279,14 @@
     <row r="148" spans="4:17" x14ac:dyDescent="0.2">
       <c r="G148" s="6"/>
       <c r="I148" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J148" s="2"/>
       <c r="K148" s="2"/>
       <c r="L148" s="2"/>
       <c r="M148" s="2"/>
       <c r="N148" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" s="2"/>
@@ -10400,10 +10294,10 @@
     </row>
     <row r="149" spans="4:17" x14ac:dyDescent="0.2">
       <c r="E149" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="G149" s="6" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="I149" s="47" cm="1">
         <f t="array" ref="I149:L150">MMULT(_xlfn.ANCHORARRAY(I59),_xlfn.MUNIT(4)*V9:V12)</f>
@@ -10435,10 +10329,10 @@
     </row>
     <row r="150" spans="4:17" x14ac:dyDescent="0.2">
       <c r="E150" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I150" s="47">
         <v>0</v>
@@ -10496,7 +10390,7 @@
   <sheetData>
     <row r="1" spans="1:22" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10505,40 +10399,40 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="I1" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -10546,16 +10440,16 @@
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="I2" s="5" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
@@ -10567,7 +10461,7 @@
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -10579,16 +10473,16 @@
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="5" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:22" s="5" customFormat="1" ht="32" x14ac:dyDescent="0.2">
@@ -10596,7 +10490,7 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -10608,7 +10502,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
@@ -10620,14 +10514,14 @@
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="G6" s="4"/>
       <c r="S6" s="5" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:22" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -10638,29 +10532,29 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="N8" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -10693,13 +10587,13 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -10732,13 +10626,13 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -10771,13 +10665,13 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -10825,7 +10719,7 @@
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="G14" s="6"/>
       <c r="I14" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -10836,23 +10730,21 @@
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
-      <c r="S14" s="2" t="s">
-        <v>69</v>
-      </c>
+      <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="V14" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I15" s="43">
         <v>1240653451807.9199</v>
@@ -10872,12 +10764,8 @@
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
-      <c r="S15" s="10">
-        <v>0</v>
-      </c>
-      <c r="T15" s="10">
-        <v>0</v>
-      </c>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
       <c r="V15" s="45">
         <f>SUM(I15:L15,S15:T15)</f>
         <v>1275532677156.157</v>
@@ -10885,13 +10773,13 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I16" s="43">
         <v>70776495966.181396</v>
@@ -10911,12 +10799,8 @@
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
-      <c r="S16" s="10">
-        <v>0</v>
-      </c>
-      <c r="T16" s="10">
-        <v>0</v>
-      </c>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
       <c r="V16" s="45">
         <f>SUM(I16:L16,S16:T16)</f>
         <v>2418662221999.3018</v>
@@ -10924,13 +10808,13 @@
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I17" s="7">
         <v>0</v>
@@ -10950,12 +10834,8 @@
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
-      <c r="S17" s="10">
-        <v>0</v>
-      </c>
-      <c r="T17" s="10">
-        <v>0</v>
-      </c>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
       <c r="V17" s="45">
         <f>SUM(I17:L17,S17:T17)</f>
         <v>63087672571000.289</v>
@@ -10963,13 +10843,13 @@
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I18" s="7">
         <v>0</v>
@@ -10989,12 +10869,8 @@
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
-      <c r="S18" s="10">
-        <v>0</v>
-      </c>
-      <c r="T18" s="10">
-        <v>0</v>
-      </c>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
       <c r="V18" s="45">
         <f>SUM(I18:L18,S18:T18)</f>
         <v>104495163828835.61</v>
@@ -11018,14 +10894,14 @@
     <row r="20" spans="1:22" x14ac:dyDescent="0.2">
       <c r="G20" s="6"/>
       <c r="I20" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -11038,10 +10914,10 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D21" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I21" s="46">
         <v>0</v>
@@ -11078,10 +10954,10 @@
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D22" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I22" s="46">
         <v>0</v>
@@ -11118,10 +10994,10 @@
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D23" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I23" s="46">
         <v>0</v>
@@ -11174,14 +11050,14 @@
     <row r="25" spans="1:22" x14ac:dyDescent="0.2">
       <c r="G25" s="6"/>
       <c r="I25" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -11194,10 +11070,10 @@
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.2">
       <c r="E26" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="I26" s="47">
         <v>0</v>
@@ -11234,10 +11110,10 @@
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="E27" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I27" s="47">
         <v>0</v>
@@ -11293,7 +11169,7 @@
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -11304,13 +11180,13 @@
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
@@ -11336,13 +11212,13 @@
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
@@ -11367,13 +11243,13 @@
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
@@ -11398,13 +11274,13 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
@@ -11450,7 +11326,7 @@
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -11461,13 +11337,13 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
@@ -11493,13 +11369,13 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
@@ -11524,13 +11400,13 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
@@ -11555,13 +11431,13 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
@@ -11605,7 +11481,7 @@
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
       <c r="N41" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" s="2"/>
@@ -11616,13 +11492,13 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
@@ -11648,13 +11524,13 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
@@ -11679,13 +11555,13 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
@@ -11710,13 +11586,13 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
@@ -11756,7 +11632,7 @@
     <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G47" s="6"/>
       <c r="I47" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
@@ -11771,13 +11647,13 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I48" s="34" cm="1">
         <f t="array" ref="I48:L51">MINVERSE(_xlfn.ANCHORARRAY(N36))</f>
@@ -11802,13 +11678,13 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I49" s="34">
         <v>-2.8985635026484349E-2</v>
@@ -11832,13 +11708,13 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I50" s="34">
         <v>0</v>
@@ -11862,13 +11738,13 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I51" s="34">
         <v>0</v>
@@ -11907,7 +11783,7 @@
     <row r="53" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G53" s="6"/>
       <c r="I53" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
@@ -11922,13 +11798,13 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I54" s="34" cm="1">
         <f t="array" ref="I54:L57">MMULT(MINVERSE(_xlfn.MUNIT(4)*V15:V18),I15:L18)</f>
@@ -11953,13 +11829,13 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I55" s="34">
         <v>2.9262662360383874E-2</v>
@@ -11983,13 +11859,13 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I56" s="34">
         <v>0</v>
@@ -12013,13 +11889,13 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I57" s="34">
         <v>0</v>
@@ -12058,14 +11934,14 @@
     <row r="59" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G59" s="6"/>
       <c r="I59" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
       <c r="N59" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" s="2"/>
@@ -12076,10 +11952,10 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D60" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I60" s="35" cm="1">
         <f t="array" ref="I60:L62">MMULT(I21:L23,MINVERSE(_xlfn.MUNIT(4)*V9:V12))</f>
@@ -12114,10 +11990,10 @@
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D61" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I61" s="35">
         <v>0</v>
@@ -12150,10 +12026,10 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D62" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I62" s="35">
         <v>0</v>
@@ -12202,14 +12078,14 @@
     <row r="64" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G64" s="6"/>
       <c r="I64" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
       <c r="N64" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
@@ -12220,10 +12096,10 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E65" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="I65" s="36" cm="1">
         <f t="array" ref="I65:L66">MMULT(I26:L27,MINVERSE(_xlfn.MUNIT(4)*V9:V12))</f>
@@ -12258,10 +12134,10 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E66" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="I66" s="36">
         <v>0</v>
@@ -12308,14 +12184,14 @@
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.2">
       <c r="I68" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
       <c r="N68" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" s="2"/>
@@ -12326,13 +12202,13 @@
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I69" s="37" cm="1">
         <f t="array" ref="I69:L72">MINVERSE(_xlfn.MUNIT(4)-MMULT(N30:Q33,I48:L51))</f>
@@ -12367,13 +12243,13 @@
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I70" s="37">
         <v>0.5136303891560563</v>
@@ -12406,13 +12282,13 @@
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I71" s="37">
         <v>0.47466429595101944</v>
@@ -12445,13 +12321,13 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I72" s="37">
         <v>0.1808607925478351</v>
@@ -12500,14 +12376,14 @@
     <row r="74" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G74" s="6"/>
       <c r="I74" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
       <c r="N74" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" s="2"/>
@@ -12518,13 +12394,13 @@
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I75" s="37" cm="1">
         <f t="array" ref="I75:L78">MMULT(_xlfn.ANCHORARRAY(N75),_xlfn.ANCHORARRAY(I48))</f>
@@ -12559,13 +12435,13 @@
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I76" s="37">
         <v>0.48869636394768912</v>
@@ -12598,13 +12474,13 @@
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I77" s="37">
         <v>0.47860034464463186</v>
@@ -12637,13 +12513,13 @@
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I78" s="37">
         <v>0.17692474385422283</v>
@@ -12690,14 +12566,14 @@
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.2">
       <c r="I80" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
       <c r="N80" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" s="2"/>
@@ -12708,13 +12584,13 @@
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I81" s="37" cm="1">
         <f t="array" ref="I81:L84">MINVERSE(_xlfn.MUNIT(4)-MMULT(N42:Q45,_xlfn.ANCHORARRAY(I54)))</f>
@@ -12749,13 +12625,13 @@
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I82" s="37">
         <v>0.28095904241499059</v>
@@ -12788,13 +12664,13 @@
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I83" s="37">
         <v>9.0865064104290842E-3</v>
@@ -12827,13 +12703,13 @@
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I84" s="37">
         <v>2.1543506163039516E-3</v>
@@ -12882,14 +12758,14 @@
     <row r="86" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G86" s="6"/>
       <c r="I86" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
       <c r="N86" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" s="2"/>
@@ -12900,13 +12776,13 @@
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I87" s="37" cm="1">
         <f t="array" ref="I87:L90">MMULT(_xlfn.ANCHORARRAY(N87),_xlfn.ANCHORARRAY(I54))</f>
@@ -12941,13 +12817,13 @@
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I88" s="37">
         <v>0.31327634984775804</v>
@@ -12980,13 +12856,13 @@
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I89" s="37">
         <v>9.015007281903447E-3</v>
@@ -13019,13 +12895,13 @@
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I90" s="37">
         <v>2.1935435784963429E-3</v>
@@ -13073,14 +12949,14 @@
     <row r="92" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G92" s="6"/>
       <c r="I92" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
       <c r="N92" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
@@ -13091,10 +12967,10 @@
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D93" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I93" s="38" cm="1">
         <f t="array" ref="I93:L95">MMULT(MMULT(_xlfn.ANCHORARRAY(N60),_xlfn.ANCHORARRAY(I48))+_xlfn.ANCHORARRAY(I60),_xlfn.ANCHORARRAY(I69))</f>
@@ -13129,10 +13005,10 @@
     </row>
     <row r="94" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D94" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I94" s="38">
         <v>0.56853731570326926</v>
@@ -13165,10 +13041,10 @@
     </row>
     <row r="95" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D95" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I95" s="38">
         <v>0.36095754025548238</v>
@@ -13217,14 +13093,14 @@
     <row r="97" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G97" s="6"/>
       <c r="I97" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
       <c r="N97" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" s="2"/>
@@ -13235,7 +13111,7 @@
     </row>
     <row r="98" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G98" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I98" s="39" cm="1">
         <f t="array" ref="I98:L98">MMULT({1,1,1},_xlfn.ANCHORARRAY(I93))</f>
@@ -13285,14 +13161,14 @@
     <row r="100" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G100" s="6"/>
       <c r="I100" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
       <c r="N100" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
@@ -13303,10 +13179,10 @@
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E101" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="I101" s="40" cm="1">
         <f t="array" ref="I101:L102">MMULT(MMULT(_xlfn.ANCHORARRAY(N65),_xlfn.ANCHORARRAY(I48))+_xlfn.ANCHORARRAY(I65),_xlfn.ANCHORARRAY(I69))</f>
@@ -13341,10 +13217,10 @@
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E102" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="I102" s="40">
         <v>26.772578939956915</v>
@@ -13392,14 +13268,14 @@
     <row r="104" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G104" s="6"/>
       <c r="I104" s="2" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="J104" s="2"/>
       <c r="K104" s="2"/>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
       <c r="N104" s="2" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" s="2"/>
@@ -13410,16 +13286,16 @@
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I105" s="38" cm="1">
         <f t="array" ref="I105:L108">MMULT(_xlfn.MUNIT(4)*N60:Q60,MMULT(_xlfn.ANCHORARRAY(I48),_xlfn.ANCHORARRAY(I69)))</f>
@@ -13454,16 +13330,16 @@
     </row>
     <row r="106" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I106" s="38">
         <v>9.7545798402333839E-3</v>
@@ -13496,16 +13372,16 @@
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I107" s="38">
         <v>2.2481686807929023E-2</v>
@@ -13538,16 +13414,16 @@
     </row>
     <row r="108" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I108" s="38">
         <v>4.575909864308894E-3</v>
@@ -13580,16 +13456,16 @@
     </row>
     <row r="109" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I109" s="38" cm="1">
         <f t="array" ref="I109:L112">MMULT(_xlfn.MUNIT(4)*N61:Q61,MMULT(_xlfn.ANCHORARRAY(I48),_xlfn.ANCHORARRAY(I69)))</f>
@@ -13624,16 +13500,16 @@
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C110" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D110" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D110" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="G110" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I110" s="38">
         <v>0.17175550335978385</v>
@@ -13666,16 +13542,16 @@
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G111" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I111" s="38">
         <v>7.2252606141233536E-2</v>
@@ -13708,16 +13584,16 @@
     </row>
     <row r="112" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C112" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D112" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D112" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="G112" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I112" s="38">
         <v>6.0449752885684167E-2</v>
@@ -13750,16 +13626,16 @@
     </row>
     <row r="113" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I113" s="38" cm="1">
         <f t="array" ref="I113:L116">MMULT(_xlfn.MUNIT(4)*N62:Q62,MMULT(_xlfn.ANCHORARRAY(I48),_xlfn.ANCHORARRAY(I69)))</f>
@@ -13794,16 +13670,16 @@
     </row>
     <row r="114" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I114" s="38">
         <v>0.10707118983802494</v>
@@ -13836,16 +13712,16 @@
     </row>
     <row r="115" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I115" s="38">
         <v>6.4517619867441409E-2</v>
@@ -13878,16 +13754,16 @@
     </row>
     <row r="116" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I116" s="38">
         <v>4.0061052887808909E-2</v>
@@ -13935,14 +13811,14 @@
     <row r="118" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G118" s="6"/>
       <c r="I118" s="2" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="J118" s="2"/>
       <c r="K118" s="2"/>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
       <c r="N118" s="2" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" s="2"/>
@@ -13953,16 +13829,16 @@
     </row>
     <row r="119" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I119" s="40" cm="1">
         <f t="array" ref="I119:L122">MMULT(_xlfn.MUNIT(4)*N65:Q65,MMULT(_xlfn.ANCHORARRAY(I48),_xlfn.ANCHORARRAY(I69)))</f>
@@ -13997,16 +13873,16 @@
     </row>
     <row r="120" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I120" s="40">
         <v>1.3229807882544642E-7</v>
@@ -14039,16 +13915,16 @@
     </row>
     <row r="121" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I121" s="40">
         <v>1.4614060327246902E-10</v>
@@ -14081,16 +13957,16 @@
     </row>
     <row r="122" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I122" s="40">
         <v>6.6703430580102092E-12</v>
@@ -14123,16 +13999,16 @@
     </row>
     <row r="123" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G123" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I123" s="48" cm="1">
         <f t="array" ref="I123:L126">MMULT(_xlfn.MUNIT(4)*N66:Q66,MMULT(_xlfn.ANCHORARRAY(I48),_xlfn.ANCHORARRAY(I69)))</f>
@@ -14167,16 +14043,16 @@
     </row>
     <row r="124" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C124" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D124" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D124" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="G124" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I124" s="48">
         <v>1.7951597344843555</v>
@@ -14209,16 +14085,16 @@
     </row>
     <row r="125" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G125" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I125" s="48">
         <v>1.4496265923147034E-3</v>
@@ -14251,16 +14127,16 @@
     </row>
     <row r="126" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C126" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D126" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D126" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="G126" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I126" s="48">
         <v>8.1939670329257829E-5</v>
@@ -14308,14 +14184,14 @@
     <row r="128" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G128" s="6"/>
       <c r="I128" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J128" s="2"/>
       <c r="K128" s="2"/>
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
       <c r="N128" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" s="2"/>
@@ -14325,10 +14201,10 @@
     </row>
     <row r="129" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D129" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G129" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I129" s="41" cm="1">
         <f t="array" ref="I129:L131">MMULT(_xlfn.ANCHORARRAY(I93),_xlfn.MUNIT(4)*MMULT(S9:T12,{1;1}))</f>
@@ -14362,10 +14238,10 @@
     </row>
     <row r="130" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D130" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I130" s="41">
         <v>337946731479.14081</v>
@@ -14397,10 +14273,10 @@
     </row>
     <row r="131" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D131" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G131" s="6" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="I131" s="41">
         <v>214558336916.19412</v>
@@ -14448,14 +14324,14 @@
     <row r="133" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G133" s="6"/>
       <c r="I133" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J133" s="2"/>
       <c r="K133" s="2"/>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
       <c r="N133" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" s="2"/>
@@ -14466,10 +14342,10 @@
     </row>
     <row r="134" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D134" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="I134" s="42" cm="1">
         <f t="array" ref="I134:L135">MMULT(_xlfn.ANCHORARRAY(I101),_xlfn.MUNIT(4)*MMULT(S9:T12,{1;1}))</f>
@@ -14504,10 +14380,10 @@
     </row>
     <row r="135" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D135" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="I135" s="42">
         <v>15914004755930.381</v>
@@ -14540,18 +14416,18 @@
     </row>
     <row r="137" spans="1:20" x14ac:dyDescent="0.2">
       <c r="N137" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="138" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I138" s="2"/>
       <c r="J138" s="2"/>
@@ -14574,13 +14450,13 @@
     </row>
     <row r="139" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G139" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I139" s="2"/>
       <c r="J139" s="2"/>
@@ -14602,13 +14478,13 @@
     </row>
     <row r="140" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I140" s="2"/>
       <c r="J140" s="2"/>
@@ -14630,13 +14506,13 @@
     </row>
     <row r="141" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G141" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I141" s="2"/>
       <c r="J141" s="2"/>
@@ -14670,7 +14546,7 @@
     <row r="143" spans="1:20" x14ac:dyDescent="0.2">
       <c r="G143" s="6"/>
       <c r="I143" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J143" s="2"/>
       <c r="K143" s="2"/>
@@ -14683,13 +14559,13 @@
     </row>
     <row r="144" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I144" s="43" cm="1">
         <f t="array" ref="I144:L147">TRANSPOSE(MMULT(MINVERSE(_xlfn.ANCHORARRAY(I48)),_xlfn.MUNIT(4)*V15:V18))</f>
@@ -14712,13 +14588,13 @@
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G145" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I145" s="43">
         <v>70776495966.181396</v>
@@ -14740,13 +14616,13 @@
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I146" s="7">
         <v>0</v>
@@ -14768,13 +14644,13 @@
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G147" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I147" s="7">
         <v>0</v>
@@ -14809,14 +14685,14 @@
     <row r="149" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G149" s="6"/>
       <c r="I149" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J149" s="2"/>
       <c r="K149" s="2"/>
       <c r="L149" s="2"/>
       <c r="M149" s="2"/>
       <c r="N149" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" s="2"/>
@@ -14824,10 +14700,10 @@
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D150" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I150" s="46" cm="1">
         <f t="array" ref="I150:L152">MMULT(_xlfn.ANCHORARRAY(I60),_xlfn.MUNIT(4)*V9:V12)</f>
@@ -14859,10 +14735,10 @@
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D151" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G151" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I151" s="46">
         <v>0</v>
@@ -14892,10 +14768,10 @@
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D152" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I152" s="46">
         <v>0</v>
@@ -14938,14 +14814,14 @@
     <row r="154" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G154" s="6"/>
       <c r="I154" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J154" s="2"/>
       <c r="K154" s="2"/>
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
       <c r="N154" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" s="2"/>
@@ -14953,10 +14829,10 @@
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E155" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="G155" s="6" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="I155" s="47" cm="1">
         <f t="array" ref="I155:L156">MMULT(_xlfn.ANCHORARRAY(I65),_xlfn.MUNIT(4)*V9:V12)</f>
@@ -14988,10 +14864,10 @@
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E156" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I156" s="47">
         <v>0</v>
@@ -15034,17 +14910,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="e67e9a88-35e1-4b39-8da9-a609eb308282" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100241E96938535DD4B921FCDFB54345D30" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c3c32a72d805f5b6b1b477f46f0cbd5b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e" xmlns:ns3="e67e9a88-35e1-4b39-8da9-a609eb308282" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8adfbf54647c461499df9b7ce19975bb" ns2:_="" ns3:_="">
     <xsd:import namespace="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e"/>
@@ -15305,6 +15170,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="e67e9a88-35e1-4b39-8da9-a609eb308282" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB3399AB-9254-4941-8CB3-3E5BD94FC575}">
   <ds:schemaRefs>
@@ -15314,17 +15190,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8F939E8-3FDD-4B79-B7F8-18DD0CA0CBEC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e"/>
-    <ds:schemaRef ds:uri="e67e9a88-35e1-4b39-8da9-a609eb308282"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C513B84B-7C74-48D1-86D3-A26BEDAA5B47}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15341,4 +15206,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8F939E8-3FDD-4B79-B7F8-18DD0CA0CBEC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e"/>
+    <ds:schemaRef ds:uri="e67e9a88-35e1-4b39-8da9-a609eb308282"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>